--- a/apiHirams/resources/templates/DRTemplate.xlsx
+++ b/apiHirams/resources/templates/DRTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Files\Program\hirams\apiHirams\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB88E847-2B4B-4763-8552-B68245E9CF8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF47C4D8-1D97-4F4E-AFA9-3B296C5F4995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,33 +37,36 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t>Assigned AO Name</t>
+    <t xml:space="preserve">                DENR-PENRO</t>
   </si>
   <si>
-    <t>Assigned AO No.</t>
+    <t xml:space="preserve">                  000-535-043-028</t>
   </si>
   <si>
-    <t>Trx code</t>
+    <t xml:space="preserve">                 Suqui, Calapan City</t>
   </si>
   <si>
-    <t>CIENT NICKNAME</t>
+    <t xml:space="preserve">                Government</t>
   </si>
   <si>
-    <t>CLIENT TIN</t>
+    <t>Jo Anne Luisttro</t>
   </si>
   <si>
-    <t>CLIENT ADDRESS</t>
+    <t>09178967101</t>
   </si>
   <si>
-    <t>CLIENT BUSINESS STYLE</t>
+    <t>5779C</t>
   </si>
   <si>
-    <t>UOM</t>
+    <t>Unit</t>
   </si>
   <si>
-    <t>ITEM NAME</t>
+    <t>DOCUMENT SCANNER</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scan speed Up to 40 ppm </t>
   </si>
 </sst>
 </file>
@@ -523,7 +526,7 @@
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -545,9 +548,6 @@
     </xf>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
@@ -568,23 +568,7 @@
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="235" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -600,15 +584,28 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1"/>
     <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="235" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="240">
@@ -1064,22 +1061,22 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="B1:AA999"/>
+  <dimension ref="B1:AA982"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" style="23" customWidth="1"/>
-    <col min="2" max="2" width="3.5546875" style="23" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" style="23" customWidth="1"/>
-    <col min="4" max="4" width="11" style="23" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="23" customWidth="1"/>
-    <col min="6" max="6" width="28.109375" style="23" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" style="23" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" style="23" customWidth="1"/>
-    <col min="9" max="9" width="1.44140625" style="23" customWidth="1"/>
-    <col min="10" max="13" width="9.109375" style="23" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" style="23" customWidth="1"/>
-    <col min="15" max="27" width="8.6640625" style="23" customWidth="1"/>
-    <col min="28" max="16384" width="14.44140625" style="23"/>
+    <col min="1" max="1" width="3.88671875" style="17" customWidth="1"/>
+    <col min="2" max="2" width="3.5546875" style="17" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" style="17" customWidth="1"/>
+    <col min="4" max="4" width="11" style="17" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="17" customWidth="1"/>
+    <col min="6" max="6" width="23.33203125" style="17" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="17" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="17" customWidth="1"/>
+    <col min="9" max="9" width="1.44140625" style="17" customWidth="1"/>
+    <col min="10" max="13" width="9.109375" style="17" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="17" customWidth="1"/>
+    <col min="15" max="27" width="8.6640625" style="17" customWidth="1"/>
+    <col min="28" max="16384" width="14.44140625" style="17"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:27" ht="26.25" customHeight="1">
@@ -1168,15 +1165,15 @@
     </row>
     <row r="4" spans="2:27" ht="20.25" customHeight="1">
       <c r="B4" s="3"/>
-      <c r="C4" s="20" t="s">
-        <v>3</v>
+      <c r="C4" s="26" t="s">
+        <v>0</v>
       </c>
-      <c r="D4" s="20"/>
+      <c r="D4" s="4"/>
       <c r="E4" s="4"/>
       <c r="F4" s="4"/>
-      <c r="G4" s="18"/>
-      <c r="H4" s="24"/>
-      <c r="I4" s="24"/>
+      <c r="G4" s="30"/>
+      <c r="H4" s="31"/>
+      <c r="I4" s="31"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -1198,10 +1195,10 @@
     </row>
     <row r="5" spans="2:27" ht="25.5" customHeight="1">
       <c r="B5" s="3"/>
-      <c r="C5" s="21" t="s">
-        <v>4</v>
+      <c r="C5" s="27" t="s">
+        <v>1</v>
       </c>
-      <c r="D5" s="21"/>
+      <c r="D5" s="4"/>
       <c r="E5" s="4"/>
       <c r="F5" s="4"/>
       <c r="G5" s="5"/>
@@ -1228,10 +1225,10 @@
     </row>
     <row r="6" spans="2:27" ht="24" customHeight="1">
       <c r="B6" s="3"/>
-      <c r="C6" s="22" t="s">
-        <v>5</v>
+      <c r="C6" s="18" t="s">
+        <v>2</v>
       </c>
-      <c r="D6" s="22"/>
+      <c r="D6" s="4"/>
       <c r="E6" s="4"/>
       <c r="F6" s="4"/>
       <c r="G6" s="5"/>
@@ -1258,10 +1255,10 @@
     </row>
     <row r="7" spans="2:27" ht="27" customHeight="1">
       <c r="B7" s="3"/>
-      <c r="C7" s="22" t="s">
-        <v>6</v>
+      <c r="C7" s="18" t="s">
+        <v>3</v>
       </c>
-      <c r="D7" s="22"/>
+      <c r="D7" s="4"/>
       <c r="E7" s="4"/>
       <c r="F7" s="4"/>
       <c r="G7" s="5"/>
@@ -1374,14 +1371,14 @@
       <c r="B11" s="7"/>
       <c r="C11" s="8"/>
       <c r="D11" s="8"/>
-      <c r="E11" s="12" t="s">
-        <v>0</v>
+      <c r="E11" s="11" t="s">
+        <v>4</v>
       </c>
-      <c r="F11" s="26" t="s">
-        <v>1</v>
+      <c r="F11" s="19" t="s">
+        <v>5</v>
       </c>
-      <c r="G11" s="16" t="s">
-        <v>2</v>
+      <c r="G11" s="15" t="s">
+        <v>6</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="2"/>
@@ -1462,11 +1459,11 @@
     </row>
     <row r="14" spans="2:27" ht="18.75" customHeight="1">
       <c r="B14" s="3"/>
-      <c r="C14" s="27"/>
-      <c r="D14" s="28"/>
-      <c r="E14" s="28"/>
-      <c r="F14" s="28"/>
-      <c r="G14" s="25"/>
+      <c r="C14" s="20"/>
+      <c r="D14" s="21"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="21"/>
+      <c r="G14" s="18"/>
       <c r="H14" s="1"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -1489,19 +1486,19 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B15" s="29">
-        <v>0</v>
+      <c r="B15" s="22">
+        <v>1</v>
       </c>
-      <c r="C15" s="30" t="s">
+      <c r="C15" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="D15" s="35" t="s">
+      <c r="D15" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="E15" s="35"/>
-      <c r="F15" s="35"/>
-      <c r="G15" s="31"/>
-      <c r="H15" s="31"/>
+      <c r="E15" s="29"/>
+      <c r="F15" s="29"/>
+      <c r="G15" s="24"/>
+      <c r="H15" s="24"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -1523,13 +1520,15 @@
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="2:27" ht="15" customHeight="1">
-      <c r="B16" s="13"/>
-      <c r="C16" s="14"/>
-      <c r="D16" s="19"/>
-      <c r="E16" s="19"/>
-      <c r="F16" s="19"/>
-      <c r="G16" s="15"/>
-      <c r="H16" s="31"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="13"/>
+      <c r="D16" s="32" t="s">
+        <v>9</v>
+      </c>
+      <c r="E16" s="32"/>
+      <c r="F16" s="32"/>
+      <c r="G16" s="14"/>
+      <c r="H16" s="24"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -1550,11 +1549,12 @@
       <c r="Z16" s="2"/>
       <c r="AA16" s="2"/>
     </row>
-    <row r="17" spans="2:27" ht="15" customHeight="1">
-      <c r="D17" s="19"/>
-      <c r="E17" s="19"/>
-      <c r="F17" s="19"/>
-      <c r="H17" s="27"/>
+    <row r="17" spans="2:27" ht="17.25" customHeight="1">
+      <c r="D17" s="33"/>
+      <c r="E17" s="33"/>
+      <c r="F17" s="33"/>
+      <c r="G17" s="2"/>
+      <c r="H17" s="24"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -1576,13 +1576,11 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B18" s="29"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="19"/>
-      <c r="E18" s="19"/>
-      <c r="F18" s="19"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="31"/>
+      <c r="D18" s="28"/>
+      <c r="E18" s="6"/>
+      <c r="F18" s="28"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="1"/>
       <c r="I18" s="2"/>
       <c r="J18" s="2"/>
       <c r="K18" s="2"/>
@@ -1604,13 +1602,8 @@
       <c r="AA18" s="2"/>
     </row>
     <row r="19" spans="2:27" ht="15" customHeight="1">
-      <c r="B19" s="13"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="19"/>
-      <c r="E19" s="19"/>
-      <c r="F19" s="19"/>
-      <c r="G19" s="15"/>
-      <c r="H19" s="31"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="25"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -1631,11 +1624,9 @@
       <c r="Z19" s="2"/>
       <c r="AA19" s="2"/>
     </row>
-    <row r="20" spans="2:27" ht="15" customHeight="1">
-      <c r="D20" s="19"/>
-      <c r="E20" s="19"/>
-      <c r="F20" s="19"/>
-      <c r="H20" s="27"/>
+    <row r="20" spans="2:27" ht="12.75" customHeight="1">
+      <c r="G20" s="10"/>
+      <c r="H20" s="20"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -1656,14 +1647,15 @@
       <c r="Z20" s="2"/>
       <c r="AA20" s="2"/>
     </row>
-    <row r="21" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="19"/>
-      <c r="E21" s="19"/>
-      <c r="F21" s="19"/>
-      <c r="H21" s="31"/>
-      <c r="I21" s="2"/>
+    <row r="21" spans="2:27" ht="15.75" customHeight="1">
+      <c r="B21" s="16"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="20"/>
+      <c r="I21" s="1"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
@@ -1683,14 +1675,14 @@
       <c r="Z21" s="2"/>
       <c r="AA21" s="2"/>
     </row>
-    <row r="22" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B22" s="28"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="19"/>
-      <c r="E22" s="19"/>
-      <c r="F22" s="19"/>
-      <c r="G22" s="33"/>
-      <c r="H22" s="31"/>
+    <row r="22" spans="2:27" ht="17.25" customHeight="1">
+      <c r="B22" s="16"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="20"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -1711,12 +1703,14 @@
       <c r="Z22" s="2"/>
       <c r="AA22" s="2"/>
     </row>
-    <row r="23" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="19"/>
-      <c r="E23" s="19"/>
-      <c r="F23" s="19"/>
+    <row r="23" spans="2:27" ht="4.5" customHeight="1">
+      <c r="B23" s="16"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="1"/>
       <c r="I23" s="2"/>
       <c r="J23" s="2"/>
       <c r="K23" s="2"/>
@@ -1737,12 +1731,14 @@
       <c r="Z23" s="2"/>
       <c r="AA23" s="2"/>
     </row>
-    <row r="24" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="19"/>
-      <c r="E24" s="19"/>
-      <c r="F24" s="19"/>
+    <row r="24" spans="2:27" ht="21" customHeight="1">
+      <c r="B24" s="16"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="1"/>
       <c r="I24" s="2"/>
       <c r="J24" s="2"/>
       <c r="K24" s="2"/>
@@ -1763,12 +1759,14 @@
       <c r="Z24" s="2"/>
       <c r="AA24" s="2"/>
     </row>
-    <row r="25" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="19"/>
-      <c r="E25" s="19"/>
-      <c r="F25" s="19"/>
+    <row r="25" spans="2:27" ht="15.75" customHeight="1">
+      <c r="B25" s="1"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="20"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -1790,33 +1788,41 @@
       <c r="AA25" s="2"/>
     </row>
     <row r="26" spans="2:27" ht="12.75" customHeight="1">
-      <c r="D26" s="19"/>
-      <c r="E26" s="19"/>
-      <c r="F26" s="19"/>
+      <c r="B26" s="1"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="20"/>
       <c r="I26" s="2"/>
-      <c r="J26" s="10"/>
-      <c r="K26" s="10"/>
-      <c r="L26" s="10"/>
-      <c r="M26" s="10"/>
-      <c r="N26" s="10"/>
-      <c r="O26" s="10"/>
-      <c r="P26" s="10"/>
-      <c r="Q26" s="10"/>
-      <c r="R26" s="10"/>
-      <c r="S26" s="10"/>
-      <c r="T26" s="10"/>
-      <c r="U26" s="10"/>
-      <c r="V26" s="10"/>
-      <c r="W26" s="10"/>
-      <c r="X26" s="10"/>
-      <c r="Y26" s="10"/>
-      <c r="Z26" s="10"/>
-      <c r="AA26" s="10"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+      <c r="V26" s="2"/>
+      <c r="W26" s="2"/>
+      <c r="X26" s="2"/>
+      <c r="Y26" s="2"/>
+      <c r="Z26" s="2"/>
+      <c r="AA26" s="2"/>
     </row>
     <row r="27" spans="2:27" ht="12.75" customHeight="1">
-      <c r="D27" s="19"/>
-      <c r="E27" s="19"/>
-      <c r="F27" s="19"/>
+      <c r="B27" s="1"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="1"/>
       <c r="I27" s="2"/>
       <c r="J27" s="2"/>
       <c r="K27" s="2"/>
@@ -1837,12 +1843,14 @@
       <c r="Z27" s="2"/>
       <c r="AA27" s="2"/>
     </row>
-    <row r="28" spans="2:27" ht="12.75" customHeight="1">
-      <c r="D28" s="19"/>
-      <c r="E28" s="19"/>
-      <c r="F28" s="19"/>
-      <c r="G28" s="1"/>
-      <c r="H28" s="31"/>
+    <row r="28" spans="2:27" ht="8.25" customHeight="1">
+      <c r="B28" s="1"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="1"/>
       <c r="I28" s="2"/>
       <c r="J28" s="2"/>
       <c r="K28" s="2"/>
@@ -1864,13 +1872,13 @@
       <c r="AA28" s="2"/>
     </row>
     <row r="29" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B29" s="13"/>
-      <c r="C29" s="14"/>
-      <c r="D29" s="19"/>
-      <c r="E29" s="19"/>
-      <c r="F29" s="19"/>
-      <c r="G29" s="1"/>
-      <c r="H29" s="31"/>
+      <c r="B29" s="1"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="20"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -1891,40 +1899,42 @@
       <c r="Z29" s="2"/>
       <c r="AA29" s="2"/>
     </row>
-    <row r="30" spans="2:27" ht="15" customHeight="1">
-      <c r="B30" s="13"/>
-      <c r="C30" s="14"/>
-      <c r="D30" s="19"/>
-      <c r="E30" s="19"/>
-      <c r="F30" s="19"/>
-      <c r="G30" s="1"/>
-      <c r="H30" s="31"/>
+    <row r="30" spans="2:27" ht="12.75" customHeight="1">
+      <c r="B30" s="1"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="1"/>
       <c r="I30" s="2"/>
-      <c r="J30" s="1"/>
-      <c r="K30" s="1"/>
-      <c r="L30" s="1"/>
-      <c r="M30" s="1"/>
-      <c r="N30" s="1"/>
-      <c r="O30" s="1"/>
-      <c r="P30" s="1"/>
-      <c r="Q30" s="1"/>
-      <c r="R30" s="1"/>
-      <c r="S30" s="1"/>
-      <c r="T30" s="1"/>
-      <c r="U30" s="1"/>
-      <c r="V30" s="1"/>
-      <c r="W30" s="1"/>
-      <c r="X30" s="1"/>
-      <c r="Y30" s="1"/>
-      <c r="Z30" s="1"/>
-      <c r="AA30" s="1"/>
-    </row>
-    <row r="31" spans="2:27" ht="15" customHeight="1">
-      <c r="D31" s="19"/>
-      <c r="E31" s="19"/>
-      <c r="F31" s="19"/>
-      <c r="G31" s="27"/>
-      <c r="H31" s="31"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
+      <c r="V30" s="2"/>
+      <c r="W30" s="2"/>
+      <c r="X30" s="2"/>
+      <c r="Y30" s="2"/>
+      <c r="Z30" s="2"/>
+      <c r="AA30" s="2"/>
+    </row>
+    <row r="31" spans="2:27" ht="12.75" customHeight="1">
+      <c r="B31" s="1"/>
+      <c r="C31" s="2"/>
+      <c r="D31" s="2"/>
+      <c r="E31" s="2"/>
+      <c r="F31" s="2"/>
+      <c r="G31" s="2"/>
+      <c r="H31" s="1"/>
       <c r="I31" s="2"/>
       <c r="J31" s="2"/>
       <c r="K31" s="2"/>
@@ -1946,9 +1956,13 @@
       <c r="AA31" s="2"/>
     </row>
     <row r="32" spans="2:27" ht="12.75" customHeight="1">
-      <c r="D32" s="19"/>
-      <c r="E32" s="19"/>
-      <c r="F32" s="19"/>
+      <c r="B32" s="1"/>
+      <c r="C32" s="2"/>
+      <c r="D32" s="2"/>
+      <c r="E32" s="2"/>
+      <c r="F32" s="2"/>
+      <c r="G32" s="2"/>
+      <c r="H32" s="1"/>
       <c r="I32" s="2"/>
       <c r="J32" s="2"/>
       <c r="K32" s="2"/>
@@ -1969,14 +1983,14 @@
       <c r="Z32" s="2"/>
       <c r="AA32" s="2"/>
     </row>
-    <row r="33" spans="2:27" ht="17.25" customHeight="1">
-      <c r="B33" s="13"/>
-      <c r="C33" s="14"/>
-      <c r="D33" s="19"/>
-      <c r="E33" s="19"/>
-      <c r="F33" s="19"/>
-      <c r="G33" s="1"/>
-      <c r="H33" s="31"/>
+    <row r="33" spans="2:27" ht="12.75" customHeight="1">
+      <c r="B33" s="1"/>
+      <c r="C33" s="2"/>
+      <c r="D33" s="2"/>
+      <c r="E33" s="2"/>
+      <c r="F33" s="2"/>
+      <c r="G33" s="2"/>
+      <c r="H33" s="1"/>
       <c r="I33" s="2"/>
       <c r="J33" s="2"/>
       <c r="K33" s="2"/>
@@ -1997,12 +2011,14 @@
       <c r="Z33" s="2"/>
       <c r="AA33" s="2"/>
     </row>
-    <row r="34" spans="2:27" ht="17.25" customHeight="1">
-      <c r="D34" s="19"/>
-      <c r="E34" s="19"/>
-      <c r="F34" s="19"/>
+    <row r="34" spans="2:27" ht="12.75" customHeight="1">
+      <c r="B34" s="1"/>
+      <c r="C34" s="2"/>
+      <c r="D34" s="2"/>
+      <c r="E34" s="2"/>
+      <c r="F34" s="2"/>
       <c r="G34" s="2"/>
-      <c r="H34" s="31"/>
+      <c r="H34" s="1"/>
       <c r="I34" s="2"/>
       <c r="J34" s="2"/>
       <c r="K34" s="2"/>
@@ -2024,9 +2040,11 @@
       <c r="AA34" s="2"/>
     </row>
     <row r="35" spans="2:27" ht="12.75" customHeight="1">
-      <c r="D35" s="19"/>
-      <c r="E35" s="19"/>
-      <c r="F35" s="19"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="2"/>
+      <c r="D35" s="2"/>
+      <c r="E35" s="2"/>
+      <c r="F35" s="2"/>
       <c r="G35" s="2"/>
       <c r="H35" s="1"/>
       <c r="I35" s="2"/>
@@ -2049,12 +2067,14 @@
       <c r="Z35" s="2"/>
       <c r="AA35" s="2"/>
     </row>
-    <row r="36" spans="2:27" ht="15" customHeight="1">
-      <c r="D36" s="19"/>
-      <c r="E36" s="19"/>
-      <c r="F36" s="19"/>
-      <c r="G36" s="1"/>
-      <c r="H36" s="34"/>
+    <row r="36" spans="2:27" ht="12.75" customHeight="1">
+      <c r="B36" s="1"/>
+      <c r="C36" s="2"/>
+      <c r="D36" s="2"/>
+      <c r="E36" s="2"/>
+      <c r="F36" s="2"/>
+      <c r="G36" s="2"/>
+      <c r="H36" s="1"/>
       <c r="I36" s="2"/>
       <c r="J36" s="2"/>
       <c r="K36" s="2"/>
@@ -2076,11 +2096,13 @@
       <c r="AA36" s="2"/>
     </row>
     <row r="37" spans="2:27" ht="12.75" customHeight="1">
-      <c r="D37" s="19"/>
-      <c r="E37" s="19"/>
-      <c r="F37" s="19"/>
-      <c r="G37" s="11"/>
-      <c r="H37" s="27"/>
+      <c r="B37" s="1"/>
+      <c r="C37" s="2"/>
+      <c r="D37" s="2"/>
+      <c r="E37" s="2"/>
+      <c r="F37" s="2"/>
+      <c r="G37" s="2"/>
+      <c r="H37" s="1"/>
       <c r="I37" s="2"/>
       <c r="J37" s="2"/>
       <c r="K37" s="2"/>
@@ -2101,15 +2123,15 @@
       <c r="Z37" s="2"/>
       <c r="AA37" s="2"/>
     </row>
-    <row r="38" spans="2:27" ht="15.75" customHeight="1">
-      <c r="B38" s="17"/>
-      <c r="C38" s="11"/>
-      <c r="D38" s="19"/>
-      <c r="E38" s="19"/>
-      <c r="F38" s="19"/>
-      <c r="G38" s="11"/>
-      <c r="H38" s="27"/>
-      <c r="I38" s="1"/>
+    <row r="38" spans="2:27" ht="12.75" customHeight="1">
+      <c r="B38" s="1"/>
+      <c r="C38" s="2"/>
+      <c r="D38" s="2"/>
+      <c r="E38" s="2"/>
+      <c r="F38" s="2"/>
+      <c r="G38" s="2"/>
+      <c r="H38" s="1"/>
+      <c r="I38" s="2"/>
       <c r="J38" s="2"/>
       <c r="K38" s="2"/>
       <c r="L38" s="2"/>
@@ -2129,14 +2151,14 @@
       <c r="Z38" s="2"/>
       <c r="AA38" s="2"/>
     </row>
-    <row r="39" spans="2:27" ht="17.25" customHeight="1">
-      <c r="B39" s="17"/>
+    <row r="39" spans="2:27" ht="12.75" customHeight="1">
+      <c r="B39" s="1"/>
       <c r="C39" s="2"/>
-      <c r="D39" s="19"/>
-      <c r="E39" s="19"/>
-      <c r="F39" s="19"/>
+      <c r="D39" s="2"/>
+      <c r="E39" s="2"/>
+      <c r="F39" s="2"/>
       <c r="G39" s="2"/>
-      <c r="H39" s="27"/>
+      <c r="H39" s="1"/>
       <c r="I39" s="2"/>
       <c r="J39" s="2"/>
       <c r="K39" s="2"/>
@@ -2157,8 +2179,8 @@
       <c r="Z39" s="2"/>
       <c r="AA39" s="2"/>
     </row>
-    <row r="40" spans="2:27" ht="4.5" customHeight="1">
-      <c r="B40" s="17"/>
+    <row r="40" spans="2:27" ht="12.75" customHeight="1">
+      <c r="B40" s="1"/>
       <c r="C40" s="2"/>
       <c r="D40" s="2"/>
       <c r="E40" s="2"/>
@@ -2185,8 +2207,8 @@
       <c r="Z40" s="2"/>
       <c r="AA40" s="2"/>
     </row>
-    <row r="41" spans="2:27" ht="21" customHeight="1">
-      <c r="B41" s="17"/>
+    <row r="41" spans="2:27" ht="12.75" customHeight="1">
+      <c r="B41" s="1"/>
       <c r="C41" s="2"/>
       <c r="D41" s="2"/>
       <c r="E41" s="2"/>
@@ -2213,14 +2235,14 @@
       <c r="Z41" s="2"/>
       <c r="AA41" s="2"/>
     </row>
-    <row r="42" spans="2:27" ht="15.75" customHeight="1">
+    <row r="42" spans="2:27" ht="12.75" customHeight="1">
       <c r="B42" s="1"/>
       <c r="C42" s="2"/>
       <c r="D42" s="2"/>
       <c r="E42" s="2"/>
       <c r="F42" s="2"/>
       <c r="G42" s="2"/>
-      <c r="H42" s="27"/>
+      <c r="H42" s="1"/>
       <c r="I42" s="2"/>
       <c r="J42" s="2"/>
       <c r="K42" s="2"/>
@@ -2248,7 +2270,7 @@
       <c r="E43" s="2"/>
       <c r="F43" s="2"/>
       <c r="G43" s="2"/>
-      <c r="H43" s="27"/>
+      <c r="H43" s="1"/>
       <c r="I43" s="2"/>
       <c r="J43" s="2"/>
       <c r="K43" s="2"/>
@@ -2297,7 +2319,7 @@
       <c r="Z44" s="2"/>
       <c r="AA44" s="2"/>
     </row>
-    <row r="45" spans="2:27" ht="8.25" customHeight="1">
+    <row r="45" spans="2:27" ht="12.75" customHeight="1">
       <c r="B45" s="1"/>
       <c r="C45" s="2"/>
       <c r="D45" s="2"/>
@@ -2332,7 +2354,7 @@
       <c r="E46" s="2"/>
       <c r="F46" s="2"/>
       <c r="G46" s="2"/>
-      <c r="H46" s="27"/>
+      <c r="H46" s="1"/>
       <c r="I46" s="2"/>
       <c r="J46" s="2"/>
       <c r="K46" s="2"/>
@@ -28561,514 +28583,12 @@
       <c r="Z982" s="2"/>
       <c r="AA982" s="2"/>
     </row>
-    <row r="983" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B983" s="1"/>
-      <c r="C983" s="2"/>
-      <c r="D983" s="2"/>
-      <c r="E983" s="2"/>
-      <c r="F983" s="2"/>
-      <c r="G983" s="2"/>
-      <c r="H983" s="1"/>
-      <c r="I983" s="2"/>
-      <c r="J983" s="2"/>
-      <c r="K983" s="2"/>
-      <c r="L983" s="2"/>
-      <c r="M983" s="2"/>
-      <c r="N983" s="2"/>
-      <c r="O983" s="2"/>
-      <c r="P983" s="2"/>
-      <c r="Q983" s="2"/>
-      <c r="R983" s="2"/>
-      <c r="S983" s="2"/>
-      <c r="T983" s="2"/>
-      <c r="U983" s="2"/>
-      <c r="V983" s="2"/>
-      <c r="W983" s="2"/>
-      <c r="X983" s="2"/>
-      <c r="Y983" s="2"/>
-      <c r="Z983" s="2"/>
-      <c r="AA983" s="2"/>
-    </row>
-    <row r="984" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B984" s="1"/>
-      <c r="C984" s="2"/>
-      <c r="D984" s="2"/>
-      <c r="E984" s="2"/>
-      <c r="F984" s="2"/>
-      <c r="G984" s="2"/>
-      <c r="H984" s="1"/>
-      <c r="I984" s="2"/>
-      <c r="J984" s="2"/>
-      <c r="K984" s="2"/>
-      <c r="L984" s="2"/>
-      <c r="M984" s="2"/>
-      <c r="N984" s="2"/>
-      <c r="O984" s="2"/>
-      <c r="P984" s="2"/>
-      <c r="Q984" s="2"/>
-      <c r="R984" s="2"/>
-      <c r="S984" s="2"/>
-      <c r="T984" s="2"/>
-      <c r="U984" s="2"/>
-      <c r="V984" s="2"/>
-      <c r="W984" s="2"/>
-      <c r="X984" s="2"/>
-      <c r="Y984" s="2"/>
-      <c r="Z984" s="2"/>
-      <c r="AA984" s="2"/>
-    </row>
-    <row r="985" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B985" s="1"/>
-      <c r="C985" s="2"/>
-      <c r="D985" s="2"/>
-      <c r="E985" s="2"/>
-      <c r="F985" s="2"/>
-      <c r="G985" s="2"/>
-      <c r="H985" s="1"/>
-      <c r="I985" s="2"/>
-      <c r="J985" s="2"/>
-      <c r="K985" s="2"/>
-      <c r="L985" s="2"/>
-      <c r="M985" s="2"/>
-      <c r="N985" s="2"/>
-      <c r="O985" s="2"/>
-      <c r="P985" s="2"/>
-      <c r="Q985" s="2"/>
-      <c r="R985" s="2"/>
-      <c r="S985" s="2"/>
-      <c r="T985" s="2"/>
-      <c r="U985" s="2"/>
-      <c r="V985" s="2"/>
-      <c r="W985" s="2"/>
-      <c r="X985" s="2"/>
-      <c r="Y985" s="2"/>
-      <c r="Z985" s="2"/>
-      <c r="AA985" s="2"/>
-    </row>
-    <row r="986" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B986" s="1"/>
-      <c r="C986" s="2"/>
-      <c r="D986" s="2"/>
-      <c r="E986" s="2"/>
-      <c r="F986" s="2"/>
-      <c r="G986" s="2"/>
-      <c r="H986" s="1"/>
-      <c r="I986" s="2"/>
-      <c r="J986" s="2"/>
-      <c r="K986" s="2"/>
-      <c r="L986" s="2"/>
-      <c r="M986" s="2"/>
-      <c r="N986" s="2"/>
-      <c r="O986" s="2"/>
-      <c r="P986" s="2"/>
-      <c r="Q986" s="2"/>
-      <c r="R986" s="2"/>
-      <c r="S986" s="2"/>
-      <c r="T986" s="2"/>
-      <c r="U986" s="2"/>
-      <c r="V986" s="2"/>
-      <c r="W986" s="2"/>
-      <c r="X986" s="2"/>
-      <c r="Y986" s="2"/>
-      <c r="Z986" s="2"/>
-      <c r="AA986" s="2"/>
-    </row>
-    <row r="987" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B987" s="1"/>
-      <c r="C987" s="2"/>
-      <c r="D987" s="2"/>
-      <c r="E987" s="2"/>
-      <c r="F987" s="2"/>
-      <c r="G987" s="2"/>
-      <c r="H987" s="1"/>
-      <c r="I987" s="2"/>
-      <c r="J987" s="2"/>
-      <c r="K987" s="2"/>
-      <c r="L987" s="2"/>
-      <c r="M987" s="2"/>
-      <c r="N987" s="2"/>
-      <c r="O987" s="2"/>
-      <c r="P987" s="2"/>
-      <c r="Q987" s="2"/>
-      <c r="R987" s="2"/>
-      <c r="S987" s="2"/>
-      <c r="T987" s="2"/>
-      <c r="U987" s="2"/>
-      <c r="V987" s="2"/>
-      <c r="W987" s="2"/>
-      <c r="X987" s="2"/>
-      <c r="Y987" s="2"/>
-      <c r="Z987" s="2"/>
-      <c r="AA987" s="2"/>
-    </row>
-    <row r="988" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B988" s="1"/>
-      <c r="C988" s="2"/>
-      <c r="D988" s="2"/>
-      <c r="E988" s="2"/>
-      <c r="F988" s="2"/>
-      <c r="G988" s="2"/>
-      <c r="H988" s="1"/>
-      <c r="I988" s="2"/>
-      <c r="J988" s="2"/>
-      <c r="K988" s="2"/>
-      <c r="L988" s="2"/>
-      <c r="M988" s="2"/>
-      <c r="N988" s="2"/>
-      <c r="O988" s="2"/>
-      <c r="P988" s="2"/>
-      <c r="Q988" s="2"/>
-      <c r="R988" s="2"/>
-      <c r="S988" s="2"/>
-      <c r="T988" s="2"/>
-      <c r="U988" s="2"/>
-      <c r="V988" s="2"/>
-      <c r="W988" s="2"/>
-      <c r="X988" s="2"/>
-      <c r="Y988" s="2"/>
-      <c r="Z988" s="2"/>
-      <c r="AA988" s="2"/>
-    </row>
-    <row r="989" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B989" s="1"/>
-      <c r="C989" s="2"/>
-      <c r="D989" s="2"/>
-      <c r="E989" s="2"/>
-      <c r="F989" s="2"/>
-      <c r="G989" s="2"/>
-      <c r="H989" s="1"/>
-      <c r="I989" s="2"/>
-      <c r="J989" s="2"/>
-      <c r="K989" s="2"/>
-      <c r="L989" s="2"/>
-      <c r="M989" s="2"/>
-      <c r="N989" s="2"/>
-      <c r="O989" s="2"/>
-      <c r="P989" s="2"/>
-      <c r="Q989" s="2"/>
-      <c r="R989" s="2"/>
-      <c r="S989" s="2"/>
-      <c r="T989" s="2"/>
-      <c r="U989" s="2"/>
-      <c r="V989" s="2"/>
-      <c r="W989" s="2"/>
-      <c r="X989" s="2"/>
-      <c r="Y989" s="2"/>
-      <c r="Z989" s="2"/>
-      <c r="AA989" s="2"/>
-    </row>
-    <row r="990" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B990" s="1"/>
-      <c r="C990" s="2"/>
-      <c r="D990" s="2"/>
-      <c r="E990" s="2"/>
-      <c r="F990" s="2"/>
-      <c r="G990" s="2"/>
-      <c r="H990" s="1"/>
-      <c r="I990" s="2"/>
-      <c r="J990" s="2"/>
-      <c r="K990" s="2"/>
-      <c r="L990" s="2"/>
-      <c r="M990" s="2"/>
-      <c r="N990" s="2"/>
-      <c r="O990" s="2"/>
-      <c r="P990" s="2"/>
-      <c r="Q990" s="2"/>
-      <c r="R990" s="2"/>
-      <c r="S990" s="2"/>
-      <c r="T990" s="2"/>
-      <c r="U990" s="2"/>
-      <c r="V990" s="2"/>
-      <c r="W990" s="2"/>
-      <c r="X990" s="2"/>
-      <c r="Y990" s="2"/>
-      <c r="Z990" s="2"/>
-      <c r="AA990" s="2"/>
-    </row>
-    <row r="991" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B991" s="1"/>
-      <c r="C991" s="2"/>
-      <c r="D991" s="2"/>
-      <c r="E991" s="2"/>
-      <c r="F991" s="2"/>
-      <c r="G991" s="2"/>
-      <c r="H991" s="1"/>
-      <c r="I991" s="2"/>
-      <c r="J991" s="2"/>
-      <c r="K991" s="2"/>
-      <c r="L991" s="2"/>
-      <c r="M991" s="2"/>
-      <c r="N991" s="2"/>
-      <c r="O991" s="2"/>
-      <c r="P991" s="2"/>
-      <c r="Q991" s="2"/>
-      <c r="R991" s="2"/>
-      <c r="S991" s="2"/>
-      <c r="T991" s="2"/>
-      <c r="U991" s="2"/>
-      <c r="V991" s="2"/>
-      <c r="W991" s="2"/>
-      <c r="X991" s="2"/>
-      <c r="Y991" s="2"/>
-      <c r="Z991" s="2"/>
-      <c r="AA991" s="2"/>
-    </row>
-    <row r="992" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B992" s="1"/>
-      <c r="C992" s="2"/>
-      <c r="D992" s="2"/>
-      <c r="E992" s="2"/>
-      <c r="F992" s="2"/>
-      <c r="G992" s="2"/>
-      <c r="H992" s="1"/>
-      <c r="I992" s="2"/>
-      <c r="J992" s="2"/>
-      <c r="K992" s="2"/>
-      <c r="L992" s="2"/>
-      <c r="M992" s="2"/>
-      <c r="N992" s="2"/>
-      <c r="O992" s="2"/>
-      <c r="P992" s="2"/>
-      <c r="Q992" s="2"/>
-      <c r="R992" s="2"/>
-      <c r="S992" s="2"/>
-      <c r="T992" s="2"/>
-      <c r="U992" s="2"/>
-      <c r="V992" s="2"/>
-      <c r="W992" s="2"/>
-      <c r="X992" s="2"/>
-      <c r="Y992" s="2"/>
-      <c r="Z992" s="2"/>
-      <c r="AA992" s="2"/>
-    </row>
-    <row r="993" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B993" s="1"/>
-      <c r="C993" s="2"/>
-      <c r="D993" s="2"/>
-      <c r="E993" s="2"/>
-      <c r="F993" s="2"/>
-      <c r="G993" s="2"/>
-      <c r="H993" s="1"/>
-      <c r="I993" s="2"/>
-      <c r="J993" s="2"/>
-      <c r="K993" s="2"/>
-      <c r="L993" s="2"/>
-      <c r="M993" s="2"/>
-      <c r="N993" s="2"/>
-      <c r="O993" s="2"/>
-      <c r="P993" s="2"/>
-      <c r="Q993" s="2"/>
-      <c r="R993" s="2"/>
-      <c r="S993" s="2"/>
-      <c r="T993" s="2"/>
-      <c r="U993" s="2"/>
-      <c r="V993" s="2"/>
-      <c r="W993" s="2"/>
-      <c r="X993" s="2"/>
-      <c r="Y993" s="2"/>
-      <c r="Z993" s="2"/>
-      <c r="AA993" s="2"/>
-    </row>
-    <row r="994" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B994" s="1"/>
-      <c r="C994" s="2"/>
-      <c r="D994" s="2"/>
-      <c r="E994" s="2"/>
-      <c r="F994" s="2"/>
-      <c r="G994" s="2"/>
-      <c r="H994" s="1"/>
-      <c r="I994" s="2"/>
-      <c r="J994" s="2"/>
-      <c r="K994" s="2"/>
-      <c r="L994" s="2"/>
-      <c r="M994" s="2"/>
-      <c r="N994" s="2"/>
-      <c r="O994" s="2"/>
-      <c r="P994" s="2"/>
-      <c r="Q994" s="2"/>
-      <c r="R994" s="2"/>
-      <c r="S994" s="2"/>
-      <c r="T994" s="2"/>
-      <c r="U994" s="2"/>
-      <c r="V994" s="2"/>
-      <c r="W994" s="2"/>
-      <c r="X994" s="2"/>
-      <c r="Y994" s="2"/>
-      <c r="Z994" s="2"/>
-      <c r="AA994" s="2"/>
-    </row>
-    <row r="995" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B995" s="1"/>
-      <c r="C995" s="2"/>
-      <c r="D995" s="2"/>
-      <c r="E995" s="2"/>
-      <c r="F995" s="2"/>
-      <c r="G995" s="2"/>
-      <c r="H995" s="1"/>
-      <c r="I995" s="2"/>
-      <c r="J995" s="2"/>
-      <c r="K995" s="2"/>
-      <c r="L995" s="2"/>
-      <c r="M995" s="2"/>
-      <c r="N995" s="2"/>
-      <c r="O995" s="2"/>
-      <c r="P995" s="2"/>
-      <c r="Q995" s="2"/>
-      <c r="R995" s="2"/>
-      <c r="S995" s="2"/>
-      <c r="T995" s="2"/>
-      <c r="U995" s="2"/>
-      <c r="V995" s="2"/>
-      <c r="W995" s="2"/>
-      <c r="X995" s="2"/>
-      <c r="Y995" s="2"/>
-      <c r="Z995" s="2"/>
-      <c r="AA995" s="2"/>
-    </row>
-    <row r="996" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B996" s="1"/>
-      <c r="C996" s="2"/>
-      <c r="D996" s="2"/>
-      <c r="E996" s="2"/>
-      <c r="F996" s="2"/>
-      <c r="G996" s="2"/>
-      <c r="H996" s="1"/>
-      <c r="I996" s="2"/>
-      <c r="J996" s="2"/>
-      <c r="K996" s="2"/>
-      <c r="L996" s="2"/>
-      <c r="M996" s="2"/>
-      <c r="N996" s="2"/>
-      <c r="O996" s="2"/>
-      <c r="P996" s="2"/>
-      <c r="Q996" s="2"/>
-      <c r="R996" s="2"/>
-      <c r="S996" s="2"/>
-      <c r="T996" s="2"/>
-      <c r="U996" s="2"/>
-      <c r="V996" s="2"/>
-      <c r="W996" s="2"/>
-      <c r="X996" s="2"/>
-      <c r="Y996" s="2"/>
-      <c r="Z996" s="2"/>
-      <c r="AA996" s="2"/>
-    </row>
-    <row r="997" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B997" s="1"/>
-      <c r="C997" s="2"/>
-      <c r="D997" s="2"/>
-      <c r="E997" s="2"/>
-      <c r="F997" s="2"/>
-      <c r="G997" s="2"/>
-      <c r="H997" s="1"/>
-      <c r="I997" s="2"/>
-      <c r="J997" s="2"/>
-      <c r="K997" s="2"/>
-      <c r="L997" s="2"/>
-      <c r="M997" s="2"/>
-      <c r="N997" s="2"/>
-      <c r="O997" s="2"/>
-      <c r="P997" s="2"/>
-      <c r="Q997" s="2"/>
-      <c r="R997" s="2"/>
-      <c r="S997" s="2"/>
-      <c r="T997" s="2"/>
-      <c r="U997" s="2"/>
-      <c r="V997" s="2"/>
-      <c r="W997" s="2"/>
-      <c r="X997" s="2"/>
-      <c r="Y997" s="2"/>
-      <c r="Z997" s="2"/>
-      <c r="AA997" s="2"/>
-    </row>
-    <row r="998" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B998" s="1"/>
-      <c r="C998" s="2"/>
-      <c r="D998" s="2"/>
-      <c r="E998" s="2"/>
-      <c r="F998" s="2"/>
-      <c r="G998" s="2"/>
-      <c r="H998" s="1"/>
-      <c r="I998" s="2"/>
-      <c r="J998" s="2"/>
-      <c r="K998" s="2"/>
-      <c r="L998" s="2"/>
-      <c r="M998" s="2"/>
-      <c r="N998" s="2"/>
-      <c r="O998" s="2"/>
-      <c r="P998" s="2"/>
-      <c r="Q998" s="2"/>
-      <c r="R998" s="2"/>
-      <c r="S998" s="2"/>
-      <c r="T998" s="2"/>
-      <c r="U998" s="2"/>
-      <c r="V998" s="2"/>
-      <c r="W998" s="2"/>
-      <c r="X998" s="2"/>
-      <c r="Y998" s="2"/>
-      <c r="Z998" s="2"/>
-      <c r="AA998" s="2"/>
-    </row>
-    <row r="999" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B999" s="1"/>
-      <c r="C999" s="2"/>
-      <c r="D999" s="2"/>
-      <c r="E999" s="2"/>
-      <c r="F999" s="2"/>
-      <c r="G999" s="2"/>
-      <c r="H999" s="1"/>
-      <c r="I999" s="2"/>
-      <c r="J999" s="2"/>
-      <c r="K999" s="2"/>
-      <c r="L999" s="2"/>
-      <c r="M999" s="2"/>
-      <c r="N999" s="2"/>
-      <c r="O999" s="2"/>
-      <c r="P999" s="2"/>
-      <c r="Q999" s="2"/>
-      <c r="R999" s="2"/>
-      <c r="S999" s="2"/>
-      <c r="T999" s="2"/>
-      <c r="U999" s="2"/>
-      <c r="V999" s="2"/>
-      <c r="W999" s="2"/>
-      <c r="X999" s="2"/>
-      <c r="Y999" s="2"/>
-      <c r="Z999" s="2"/>
-      <c r="AA999" s="2"/>
-    </row>
   </sheetData>
-  <mergeCells count="30">
-    <mergeCell ref="D39:F39"/>
-    <mergeCell ref="D34:F34"/>
-    <mergeCell ref="D35:F35"/>
-    <mergeCell ref="D36:F36"/>
-    <mergeCell ref="D37:F37"/>
-    <mergeCell ref="D38:F38"/>
-    <mergeCell ref="D27:F27"/>
-    <mergeCell ref="D28:F28"/>
-    <mergeCell ref="D17:F17"/>
-    <mergeCell ref="D20:F20"/>
-    <mergeCell ref="D21:F21"/>
-    <mergeCell ref="D22:F22"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="D25:F25"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="D29:F29"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="D31:F31"/>
-    <mergeCell ref="D32:F32"/>
-    <mergeCell ref="D33:F33"/>
-    <mergeCell ref="C7:D7"/>
+  <mergeCells count="4">
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="G4:I4"/>
-    <mergeCell ref="D19:F19"/>
-    <mergeCell ref="D18:F18"/>
     <mergeCell ref="D16:F16"/>
-    <mergeCell ref="C4:D4"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="D17:F17"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="94" orientation="portrait" r:id="rId1"/>

--- a/apiHirams/resources/templates/DRTemplate.xlsx
+++ b/apiHirams/resources/templates/DRTemplate.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\My Files\Program\hirams\apiHirams\resources\templates\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF47C4D8-1D97-4F4E-AFA9-3B296C5F4995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E8AF005-3BBF-4997-8C1A-784E1C28CF59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,18 +39,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
-    <t xml:space="preserve">                DENR-PENRO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                  000-535-043-028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                 Suqui, Calapan City</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                Government</t>
-  </si>
-  <si>
     <t>Jo Anne Luisttro</t>
   </si>
   <si>
@@ -68,6 +56,18 @@
   <si>
     <t xml:space="preserve">Scan speed Up to 40 ppm </t>
   </si>
+  <si>
+    <t>Government</t>
+  </si>
+  <si>
+    <t>Suqui, Calapan City</t>
+  </si>
+  <si>
+    <t>000-535-043-028</t>
+  </si>
+  <si>
+    <t>DENR-PENRO</t>
+  </si>
 </sst>
 </file>
 
@@ -79,7 +79,7 @@
     <numFmt numFmtId="164" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="165" formatCode="[$-409]dd\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="26">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -213,13 +213,6 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -286,7 +279,7 @@
   </borders>
   <cellStyleXfs count="240">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="17" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -328,8 +321,8 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0"/>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
@@ -520,7 +513,7 @@
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0"/>
     <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -533,13 +526,10 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
@@ -553,13 +543,13 @@
     <xf numFmtId="1" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" xfId="113" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="113" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="164" fontId="22" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="21" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -575,37 +565,42 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="164" fontId="20" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="25" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="165" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="235" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="235" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="18" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="24" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="240">
@@ -1064,19 +1059,19 @@
   <dimension ref="B1:AA982"/>
   <sheetFormatPr defaultColWidth="14.44140625" defaultRowHeight="15" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="3.88671875" style="17" customWidth="1"/>
-    <col min="2" max="2" width="3.5546875" style="17" customWidth="1"/>
-    <col min="3" max="3" width="11.5546875" style="17" customWidth="1"/>
-    <col min="4" max="4" width="11" style="17" customWidth="1"/>
-    <col min="5" max="5" width="16.6640625" style="17" customWidth="1"/>
-    <col min="6" max="6" width="23.33203125" style="17" customWidth="1"/>
-    <col min="7" max="7" width="16.6640625" style="17" customWidth="1"/>
-    <col min="8" max="8" width="15.5546875" style="17" customWidth="1"/>
-    <col min="9" max="9" width="1.44140625" style="17" customWidth="1"/>
-    <col min="10" max="13" width="9.109375" style="17" customWidth="1"/>
-    <col min="14" max="14" width="11.5546875" style="17" customWidth="1"/>
-    <col min="15" max="27" width="8.6640625" style="17" customWidth="1"/>
-    <col min="28" max="16384" width="14.44140625" style="17"/>
+    <col min="1" max="1" width="3.88671875" style="16" customWidth="1"/>
+    <col min="2" max="2" width="3.5546875" style="16" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" style="16" customWidth="1"/>
+    <col min="4" max="4" width="11" style="16" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" style="16" customWidth="1"/>
+    <col min="6" max="6" width="23.33203125" style="16" customWidth="1"/>
+    <col min="7" max="7" width="16.6640625" style="16" customWidth="1"/>
+    <col min="8" max="8" width="15.5546875" style="16" customWidth="1"/>
+    <col min="9" max="9" width="1.44140625" style="16" customWidth="1"/>
+    <col min="10" max="13" width="9.109375" style="16" customWidth="1"/>
+    <col min="14" max="14" width="11.5546875" style="16" customWidth="1"/>
+    <col min="15" max="27" width="8.6640625" style="16" customWidth="1"/>
+    <col min="28" max="16384" width="14.44140625" style="16"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:27" ht="26.25" customHeight="1">
@@ -1165,15 +1160,15 @@
     </row>
     <row r="4" spans="2:27" ht="20.25" customHeight="1">
       <c r="B4" s="3"/>
-      <c r="C4" s="26" t="s">
-        <v>0</v>
+      <c r="C4" s="32" t="s">
+        <v>9</v>
       </c>
-      <c r="D4" s="4"/>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="30"/>
-      <c r="H4" s="31"/>
-      <c r="I4" s="31"/>
+      <c r="D4" s="32"/>
+      <c r="E4" s="32"/>
+      <c r="F4" s="32"/>
+      <c r="G4" s="27"/>
+      <c r="H4" s="28"/>
+      <c r="I4" s="28"/>
       <c r="J4" s="2"/>
       <c r="K4" s="2"/>
       <c r="L4" s="2"/>
@@ -1195,15 +1190,15 @@
     </row>
     <row r="5" spans="2:27" ht="25.5" customHeight="1">
       <c r="B5" s="3"/>
-      <c r="C5" s="27" t="s">
-        <v>1</v>
+      <c r="C5" s="33" t="s">
+        <v>8</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="5"/>
-      <c r="I5" s="6"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="33"/>
+      <c r="F5" s="33"/>
+      <c r="G5" s="4"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
       <c r="J5" s="2"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
@@ -1225,15 +1220,15 @@
     </row>
     <row r="6" spans="2:27" ht="24" customHeight="1">
       <c r="B6" s="3"/>
-      <c r="C6" s="18" t="s">
-        <v>2</v>
+      <c r="C6" s="31" t="s">
+        <v>7</v>
       </c>
-      <c r="D6" s="4"/>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="5"/>
-      <c r="I6" s="6"/>
+      <c r="D6" s="31"/>
+      <c r="E6" s="31"/>
+      <c r="F6" s="31"/>
+      <c r="G6" s="4"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="5"/>
       <c r="J6" s="2"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
@@ -1255,15 +1250,15 @@
     </row>
     <row r="7" spans="2:27" ht="27" customHeight="1">
       <c r="B7" s="3"/>
-      <c r="C7" s="18" t="s">
-        <v>3</v>
+      <c r="C7" s="31" t="s">
+        <v>6</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="5"/>
-      <c r="H7" s="5"/>
-      <c r="I7" s="6"/>
+      <c r="D7" s="31"/>
+      <c r="E7" s="31"/>
+      <c r="F7" s="31"/>
+      <c r="G7" s="4"/>
+      <c r="H7" s="4"/>
+      <c r="I7" s="5"/>
       <c r="J7" s="2"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
@@ -1340,10 +1335,10 @@
       <c r="AA9" s="2"/>
     </row>
     <row r="10" spans="2:27" ht="14.25" customHeight="1">
-      <c r="B10" s="7"/>
-      <c r="C10" s="8"/>
+      <c r="B10" s="6"/>
+      <c r="C10" s="7"/>
       <c r="D10" s="2"/>
-      <c r="E10" s="9"/>
+      <c r="E10" s="8"/>
       <c r="F10" s="2"/>
       <c r="G10" s="2"/>
       <c r="H10" s="2"/>
@@ -1368,17 +1363,17 @@
       <c r="AA10" s="2"/>
     </row>
     <row r="11" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B11" s="7"/>
-      <c r="C11" s="8"/>
-      <c r="D11" s="8"/>
-      <c r="E11" s="11" t="s">
-        <v>4</v>
+      <c r="B11" s="6"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="10" t="s">
+        <v>0</v>
       </c>
-      <c r="F11" s="19" t="s">
-        <v>5</v>
+      <c r="F11" s="18" t="s">
+        <v>1</v>
       </c>
-      <c r="G11" s="15" t="s">
-        <v>6</v>
+      <c r="G11" s="14" t="s">
+        <v>2</v>
       </c>
       <c r="H11" s="1"/>
       <c r="I11" s="2"/>
@@ -1459,11 +1454,11 @@
     </row>
     <row r="14" spans="2:27" ht="18.75" customHeight="1">
       <c r="B14" s="3"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="21"/>
-      <c r="E14" s="21"/>
-      <c r="F14" s="21"/>
-      <c r="G14" s="18"/>
+      <c r="C14" s="19"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="20"/>
+      <c r="F14" s="20"/>
+      <c r="G14" s="17"/>
       <c r="H14" s="1"/>
       <c r="I14" s="2"/>
       <c r="J14" s="2"/>
@@ -1486,19 +1481,19 @@
       <c r="AA14" s="2"/>
     </row>
     <row r="15" spans="2:27" ht="12.75" customHeight="1">
-      <c r="B15" s="22">
+      <c r="B15" s="21">
         <v>1</v>
       </c>
-      <c r="C15" s="23" t="s">
-        <v>7</v>
+      <c r="C15" s="22" t="s">
+        <v>3</v>
       </c>
-      <c r="D15" s="29" t="s">
-        <v>8</v>
+      <c r="D15" s="26" t="s">
+        <v>4</v>
       </c>
-      <c r="E15" s="29"/>
-      <c r="F15" s="29"/>
-      <c r="G15" s="24"/>
-      <c r="H15" s="24"/>
+      <c r="E15" s="26"/>
+      <c r="F15" s="26"/>
+      <c r="G15" s="23"/>
+      <c r="H15" s="23"/>
       <c r="I15" s="2"/>
       <c r="J15" s="2"/>
       <c r="K15" s="2"/>
@@ -1520,15 +1515,15 @@
       <c r="AA15" s="2"/>
     </row>
     <row r="16" spans="2:27" ht="15" customHeight="1">
-      <c r="B16" s="12"/>
-      <c r="C16" s="13"/>
-      <c r="D16" s="32" t="s">
-        <v>9</v>
+      <c r="B16" s="11"/>
+      <c r="C16" s="12"/>
+      <c r="D16" s="29" t="s">
+        <v>5</v>
       </c>
-      <c r="E16" s="32"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="14"/>
-      <c r="H16" s="24"/>
+      <c r="E16" s="29"/>
+      <c r="F16" s="29"/>
+      <c r="G16" s="13"/>
+      <c r="H16" s="23"/>
       <c r="I16" s="2"/>
       <c r="J16" s="2"/>
       <c r="K16" s="2"/>
@@ -1550,11 +1545,11 @@
       <c r="AA16" s="2"/>
     </row>
     <row r="17" spans="2:27" ht="17.25" customHeight="1">
-      <c r="D17" s="33"/>
-      <c r="E17" s="33"/>
-      <c r="F17" s="33"/>
+      <c r="D17" s="30"/>
+      <c r="E17" s="30"/>
+      <c r="F17" s="30"/>
       <c r="G17" s="2"/>
-      <c r="H17" s="24"/>
+      <c r="H17" s="23"/>
       <c r="I17" s="2"/>
       <c r="J17" s="2"/>
       <c r="K17" s="2"/>
@@ -1576,9 +1571,9 @@
       <c r="AA17" s="2"/>
     </row>
     <row r="18" spans="2:27" ht="12.75" customHeight="1">
-      <c r="D18" s="28"/>
-      <c r="E18" s="6"/>
-      <c r="F18" s="28"/>
+      <c r="D18" s="25"/>
+      <c r="E18" s="5"/>
+      <c r="F18" s="25"/>
       <c r="G18" s="2"/>
       <c r="H18" s="1"/>
       <c r="I18" s="2"/>
@@ -1603,7 +1598,7 @@
     </row>
     <row r="19" spans="2:27" ht="15" customHeight="1">
       <c r="G19" s="1"/>
-      <c r="H19" s="25"/>
+      <c r="H19" s="24"/>
       <c r="I19" s="2"/>
       <c r="J19" s="2"/>
       <c r="K19" s="2"/>
@@ -1625,8 +1620,8 @@
       <c r="AA19" s="2"/>
     </row>
     <row r="20" spans="2:27" ht="12.75" customHeight="1">
-      <c r="G20" s="10"/>
-      <c r="H20" s="20"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="19"/>
       <c r="I20" s="2"/>
       <c r="J20" s="2"/>
       <c r="K20" s="2"/>
@@ -1648,13 +1643,13 @@
       <c r="AA20" s="2"/>
     </row>
     <row r="21" spans="2:27" ht="15.75" customHeight="1">
-      <c r="B21" s="16"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="20"/>
+      <c r="B21" s="15"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="19"/>
       <c r="I21" s="1"/>
       <c r="J21" s="2"/>
       <c r="K21" s="2"/>
@@ -1676,13 +1671,13 @@
       <c r="AA21" s="2"/>
     </row>
     <row r="22" spans="2:27" ht="17.25" customHeight="1">
-      <c r="B22" s="16"/>
+      <c r="B22" s="15"/>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2"/>
       <c r="G22" s="2"/>
-      <c r="H22" s="20"/>
+      <c r="H22" s="19"/>
       <c r="I22" s="2"/>
       <c r="J22" s="2"/>
       <c r="K22" s="2"/>
@@ -1704,7 +1699,7 @@
       <c r="AA22" s="2"/>
     </row>
     <row r="23" spans="2:27" ht="4.5" customHeight="1">
-      <c r="B23" s="16"/>
+      <c r="B23" s="15"/>
       <c r="C23" s="2"/>
       <c r="D23" s="2"/>
       <c r="E23" s="2"/>
@@ -1732,7 +1727,7 @@
       <c r="AA23" s="2"/>
     </row>
     <row r="24" spans="2:27" ht="21" customHeight="1">
-      <c r="B24" s="16"/>
+      <c r="B24" s="15"/>
       <c r="C24" s="2"/>
       <c r="D24" s="2"/>
       <c r="E24" s="2"/>
@@ -1766,7 +1761,7 @@
       <c r="E25" s="2"/>
       <c r="F25" s="2"/>
       <c r="G25" s="2"/>
-      <c r="H25" s="20"/>
+      <c r="H25" s="19"/>
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
@@ -1794,7 +1789,7 @@
       <c r="E26" s="2"/>
       <c r="F26" s="2"/>
       <c r="G26" s="2"/>
-      <c r="H26" s="20"/>
+      <c r="H26" s="19"/>
       <c r="I26" s="2"/>
       <c r="J26" s="2"/>
       <c r="K26" s="2"/>
@@ -1878,7 +1873,7 @@
       <c r="E29" s="2"/>
       <c r="F29" s="2"/>
       <c r="G29" s="2"/>
-      <c r="H29" s="20"/>
+      <c r="H29" s="19"/>
       <c r="I29" s="2"/>
       <c r="J29" s="2"/>
       <c r="K29" s="2"/>
@@ -28584,11 +28579,15 @@
       <c r="AA982" s="2"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="8">
     <mergeCell ref="D15:F15"/>
     <mergeCell ref="G4:I4"/>
     <mergeCell ref="D16:F16"/>
     <mergeCell ref="D17:F17"/>
+    <mergeCell ref="C4:F4"/>
+    <mergeCell ref="C5:F5"/>
+    <mergeCell ref="C6:F6"/>
+    <mergeCell ref="C7:F7"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup scale="94" orientation="portrait" r:id="rId1"/>
